--- a/source-data/Enerium_Достижения.xlsx
+++ b/source-data/Enerium_Достижения.xlsx
@@ -189,7 +189,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">e59f6b87b632b2c7 — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
+          <t xml:space="preserve">9ae132d7a59a8866 — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
         </is>
       </c>
     </row>
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="M3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O3" s="3"/>
     </row>
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="M4">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="N4">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O4" s="3"/>
     </row>
@@ -684,10 +684,10 @@
         </is>
       </c>
       <c r="M5">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="N5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O5" s="3"/>
     </row>
@@ -749,10 +749,10 @@
         </is>
       </c>
       <c r="M6">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="N6">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="O6" s="3"/>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Победить крафтового босса в Эхо</t>
+          <t xml:space="preserve">Победить в Эхо врага, призванного из мастерской</t>
         </is>
       </c>
       <c r="H29">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Победы над крафтовыми боссами</t>
+          <t xml:space="preserve">Победы над призванными врагами</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="M31">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="N31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O31" s="3"/>
     </row>
@@ -2414,11 +2414,11 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Дойти за неделю до одиннадцатой ступени Эхо — первого босса</t>
+          <t xml:space="preserve">Дойти за неделю до девятой ступени Эхо — к старшим элитам</t>
         </is>
       </c>
       <c r="H32">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2565,9 +2565,6 @@
           <t xml:space="preserve">вневременная</t>
         </is>
       </c>
-      <c r="N34">
-        <v>147</v>
-      </c>
       <c r="O34" s="3"/>
     </row>
     <row r="35">
@@ -2624,14 +2621,11 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t xml:space="preserve">древняя</t>
-        </is>
-      </c>
-      <c r="M35">
-        <v>70</v>
+          <t xml:space="preserve">вневременная</t>
+        </is>
       </c>
       <c r="N35">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="O35" s="3"/>
     </row>
@@ -4253,10 +4247,10 @@
         </is>
       </c>
       <c r="M60">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N60">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O60" s="3"/>
     </row>
@@ -4318,10 +4312,10 @@
         </is>
       </c>
       <c r="M61">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="N61">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O61" s="3"/>
     </row>
@@ -4383,10 +4377,10 @@
         </is>
       </c>
       <c r="M62">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="N62">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O62" s="3"/>
     </row>
@@ -4968,7 +4962,7 @@
         </is>
       </c>
       <c r="M71">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N71">
         <v>33</v>
@@ -5033,7 +5027,7 @@
         </is>
       </c>
       <c r="M72">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N72">
         <v>82</v>
@@ -5163,7 +5157,7 @@
         </is>
       </c>
       <c r="M74">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N74">
         <v>66</v>
@@ -5358,7 +5352,7 @@
         </is>
       </c>
       <c r="M77">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N77">
         <v>46</v>
@@ -5949,12 +5943,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Десятый раунд</t>
+          <t xml:space="preserve">Последний раунд</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Взять этаж на десятом, последнем раунде</t>
+          <t xml:space="preserve">Взять этаж в последнем раунде боя — у рядовых, элиты и босса он свой</t>
         </is>
       </c>
       <c r="H86">
@@ -6615,12 +6609,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сам себе ключник</t>
+          <t xml:space="preserve">Ключ на дне</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Создать рунные ключи в мастерской</t>
+          <t xml:space="preserve">Найти рунные ключи в сундуке, где главное — не ключи</t>
         </is>
       </c>
       <c r="H95">
@@ -6628,7 +6622,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">keyCraft</t>
+          <t xml:space="preserve">keyChest</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6641,23 +6635,23 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t xml:space="preserve">эпическая</t>
+          <t xml:space="preserve">уникальная</t>
         </is>
       </c>
       <c r="M95">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="N95">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="O95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ключ можно не только найти.</t>
+          <t xml:space="preserve">Ключ можно не только заработать.</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t xml:space="preserve">III</t>
+          <t xml:space="preserve">II</t>
         </is>
       </c>
     </row>
@@ -6987,7 +6981,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Создать пробуждённый призыв крафтового босса</t>
+          <t xml:space="preserve">Создать призыв пробуждённого босса — Забытого</t>
         </is>
       </c>
       <c r="H100">

--- a/source-data/Enerium_Достижения.xlsx
+++ b/source-data/Enerium_Достижения.xlsx
@@ -189,7 +189,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">9ae132d7a59a8866 — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
+          <t xml:space="preserve">f3608b18bcabb61a — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="M3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N3">
         <v>4</v>
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="M4">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="N4">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="O4" s="3"/>
     </row>
@@ -687,7 +687,7 @@
         <v>28</v>
       </c>
       <c r="N5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O5" s="3"/>
     </row>
@@ -749,10 +749,10 @@
         </is>
       </c>
       <c r="M6">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="N6">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="O6" s="3"/>
     </row>
@@ -1070,14 +1070,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t xml:space="preserve">эпическая</t>
+          <t xml:space="preserve">первородная</t>
         </is>
       </c>
       <c r="M11">
-        <v>36</v>
+        <v>105</v>
       </c>
       <c r="N11">
-        <v>36</v>
+        <v>105</v>
       </c>
       <c r="O11" s="3"/>
     </row>
@@ -1135,14 +1135,8 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t xml:space="preserve">древняя</t>
-        </is>
-      </c>
-      <c r="M12">
-        <v>57</v>
-      </c>
-      <c r="N12">
-        <v>57</v>
+          <t xml:space="preserve">вневременная</t>
+        </is>
       </c>
       <c r="O12" s="3"/>
     </row>
@@ -1200,14 +1194,8 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t xml:space="preserve">первородная</t>
-        </is>
-      </c>
-      <c r="M13">
-        <v>78</v>
-      </c>
-      <c r="N13">
-        <v>78</v>
+          <t xml:space="preserve">вневременная</t>
+        </is>
       </c>
       <c r="O13" s="3"/>
     </row>
@@ -1265,14 +1253,8 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t xml:space="preserve">первородная</t>
-        </is>
-      </c>
-      <c r="M14">
-        <v>98</v>
-      </c>
-      <c r="N14">
-        <v>91</v>
+          <t xml:space="preserve">вневременная</t>
+        </is>
       </c>
       <c r="O14" s="3"/>
     </row>
@@ -1464,7 +1446,7 @@
         </is>
       </c>
       <c r="M17">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="N17">
         <v>100</v>
@@ -2114,10 +2096,10 @@
         </is>
       </c>
       <c r="M27">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O27" s="3"/>
     </row>
@@ -2374,10 +2356,10 @@
         </is>
       </c>
       <c r="M31">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N31">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O31" s="3"/>
     </row>
@@ -2442,7 +2424,7 @@
         <v>14</v>
       </c>
       <c r="N32">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="O32" s="3"/>
     </row>
@@ -2503,9 +2485,6 @@
           <t xml:space="preserve">вневременная</t>
         </is>
       </c>
-      <c r="N33">
-        <v>14</v>
-      </c>
       <c r="O33" s="3"/>
     </row>
     <row r="34">
@@ -2621,11 +2600,14 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t xml:space="preserve">вневременная</t>
-        </is>
+          <t xml:space="preserve">первородная</t>
+        </is>
+      </c>
+      <c r="M35">
+        <v>105</v>
       </c>
       <c r="N35">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O35" s="3"/>
     </row>
@@ -2947,10 +2929,10 @@
         </is>
       </c>
       <c r="M40">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N40">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O40" s="3"/>
     </row>
@@ -3077,7 +3059,7 @@
         </is>
       </c>
       <c r="M42">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N42">
         <v>7</v>
@@ -3210,7 +3192,7 @@
         <v>5</v>
       </c>
       <c r="N44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O44" s="3"/>
     </row>
@@ -3593,14 +3575,8 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t xml:space="preserve">первородная</t>
-        </is>
-      </c>
-      <c r="M50">
-        <v>78</v>
-      </c>
-      <c r="N50">
-        <v>78</v>
+          <t xml:space="preserve">вневременная</t>
+        </is>
       </c>
       <c r="O50" s="3"/>
     </row>
@@ -3792,7 +3768,7 @@
         </is>
       </c>
       <c r="M53">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="N53">
         <v>21</v>
@@ -4182,10 +4158,10 @@
         </is>
       </c>
       <c r="M59">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N59">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O59" s="3"/>
     </row>
@@ -4247,10 +4223,10 @@
         </is>
       </c>
       <c r="M60">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="N60">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="O60" s="3"/>
     </row>
@@ -4308,14 +4284,14 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t xml:space="preserve">древняя</t>
+          <t xml:space="preserve">первородная</t>
         </is>
       </c>
       <c r="M61">
-        <v>66</v>
+        <v>109</v>
       </c>
       <c r="N61">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="O61" s="3"/>
     </row>
@@ -4373,14 +4349,8 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t xml:space="preserve">первородная</t>
-        </is>
-      </c>
-      <c r="M62">
-        <v>133</v>
-      </c>
-      <c r="N62">
-        <v>81</v>
+          <t xml:space="preserve">вневременная</t>
+        </is>
       </c>
       <c r="O62" s="3"/>
     </row>
@@ -4572,7 +4542,7 @@
         </is>
       </c>
       <c r="M65">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="N65">
         <v>26</v>
@@ -4633,14 +4603,8 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t xml:space="preserve">первородная</t>
-        </is>
-      </c>
-      <c r="M66">
-        <v>84</v>
-      </c>
-      <c r="N66">
-        <v>84</v>
+          <t xml:space="preserve">вневременная</t>
+        </is>
       </c>
       <c r="O66" s="3"/>
     </row>
@@ -4832,7 +4796,7 @@
         </is>
       </c>
       <c r="M69">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N69">
         <v>27</v>
@@ -5352,7 +5316,7 @@
         </is>
       </c>
       <c r="M77">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="N77">
         <v>46</v>
@@ -5485,7 +5449,7 @@
         <v>26</v>
       </c>
       <c r="N79">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O79" s="3"/>
     </row>

--- a/source-data/Enerium_Достижения.xlsx
+++ b/source-data/Enerium_Достижения.xlsx
@@ -177,7 +177,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-01 — из данных игры сборщиком tools/content-gen/tables/build.py (содержимое — tools/content-gen/tables/collect.js)</t>
+          <t xml:space="preserve">2026-10-02 — из данных игры сборщиком tools/content-gen/tables/build.py (содержимое — tools/content-gen/tables/collect.js)</t>
         </is>
       </c>
     </row>
@@ -189,7 +189,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">f3608b18bcabb61a — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
+          <t xml:space="preserve">6058f4f785406926 — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="M3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N3">
         <v>4</v>
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="M4">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="N4">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O4" s="3"/>
     </row>
@@ -659,11 +659,11 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Одолеть 10 000 элит на этажах биомов</t>
+          <t xml:space="preserve">Одолеть 12 000 элит на этажах биомов</t>
         </is>
       </c>
       <c r="H5">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -724,11 +724,11 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Одолеть 50 000 элит</t>
+          <t xml:space="preserve">Одолеть 30 000 элит</t>
         </is>
       </c>
       <c r="H6">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -745,14 +745,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t xml:space="preserve">первородная</t>
+          <t xml:space="preserve">древняя</t>
         </is>
       </c>
       <c r="M6">
-        <v>112</v>
+        <v>61</v>
       </c>
       <c r="N6">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="O6" s="3"/>
     </row>
@@ -1074,10 +1074,10 @@
         </is>
       </c>
       <c r="M11">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="N11">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="O11" s="3"/>
     </row>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="M31">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="N31">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O31" s="3"/>
     </row>
@@ -2424,7 +2424,7 @@
         <v>14</v>
       </c>
       <c r="N32">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="O32" s="3"/>
     </row>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="M35">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="N35">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="O35" s="3"/>
     </row>
@@ -2932,7 +2932,7 @@
         <v>55</v>
       </c>
       <c r="N40">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O40" s="3"/>
     </row>
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="M42">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N42">
         <v>7</v>
@@ -3768,7 +3768,7 @@
         </is>
       </c>
       <c r="M53">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="N53">
         <v>21</v>
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="M59">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N59">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O59" s="3"/>
     </row>
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="M60">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="N60">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="O60" s="3"/>
     </row>
@@ -4288,10 +4288,10 @@
         </is>
       </c>
       <c r="M61">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N61">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O61" s="3"/>
     </row>
@@ -4991,7 +4991,7 @@
         </is>
       </c>
       <c r="M72">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N72">
         <v>82</v>
@@ -5121,7 +5121,7 @@
         </is>
       </c>
       <c r="M74">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N74">
         <v>66</v>
@@ -5247,11 +5247,11 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t xml:space="preserve">эпическая</t>
+          <t xml:space="preserve">уникальная</t>
         </is>
       </c>
       <c r="M76">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N76">
         <v>16</v>
@@ -5316,7 +5316,7 @@
         </is>
       </c>
       <c r="M77">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="N77">
         <v>46</v>

--- a/source-data/Enerium_Достижения.xlsx
+++ b/source-data/Enerium_Достижения.xlsx
@@ -13,11 +13,11 @@
     <sheet name="Виды наград" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Достижения'!$A$1:$P$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Достижения'!$A$1:$R$220</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Первенства'!$A$1:$F$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Категории'!$A$1:$D$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Темы'!$A$1:$B$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Виды наград'!$A$1:$D$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Виды наград'!$A$1:$D$19</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -177,7 +177,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-02 — из данных игры сборщиком tools/content-gen/tables/build.py (содержимое — tools/content-gen/tables/collect.js)</t>
+          <t xml:space="preserve">2026-10-07 — из данных игры сборщиком tools/content-gen/tables/build.py (содержимое — tools/content-gen/tables/collect.js)</t>
         </is>
       </c>
     </row>
@@ -189,7 +189,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">6058f4f785406926 — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
+          <t xml:space="preserve">5667a82ce03aed34 — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
         </is>
       </c>
     </row>
@@ -226,7 +226,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">102 строки.</t>
+          <t xml:space="preserve">219 строк.</t>
         </is>
       </c>
     </row>
@@ -274,7 +274,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">15 строк.</t>
+          <t xml:space="preserve">18 строк.</t>
         </is>
       </c>
     </row>
@@ -304,8 +304,8 @@
 III — слабые, почти незаметные намёки — слово-отзвук без имени тайны (ADR-0022: намёки на Странника — с цикла III)
 IV — заметнее, но всё ещё намёки: иносказание, без прямых имён и формулировок тайны
 V — намёки очевиднее («начиная с 5 будут намёки»); прямого раскрытия §38 нет
-VI — только для команды: здесь тайны названы прямо
-Ступени слов: D — прямое раскрытие — только цикл VI, для команды; H3 — явный намёк — с цикла V; H2 — заметный намёк — с цикла IV; H1 — слабый намёк, слово-отзвук — с цикла III.
+VI — раскрытие: в текстах игрока цикла VI тайны могут быть названы прямо (ADR-0054); в текстах циклов I–V — нет
+Ступени слов: D — прямое раскрытие — только с цикла VI: игрок получает его в игре, раньше — нет; H3 — явный намёк — с цикла V; H2 — заметный намёк — с цикла IV; H1 — слабый намёк, слово-отзвук — с цикла III.
 Проверка — node tools/content-gen/tables/check_spoilers.js; все совпадения по циклам — «Реестр имён», лист «Намёки по циклам».</t>
         </is>
       </c>
@@ -328,7 +328,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P103"/>
+  <dimension ref="A1:R220"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -347,6 +347,8 @@
     <col min="14" max="14" width="9" customWidth="1"/>
     <col min="15" max="15" width="40" customWidth="1"/>
     <col min="16" max="16" width="7" customWidth="1"/>
+    <col min="17" max="17" width="7" customWidth="1"/>
+    <col min="18" max="18" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -430,6 +432,16 @@
           <t xml:space="preserve">С цикла</t>
         </is>
       </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Блок цикла</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Для команды</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -554,7 +566,7 @@
         </is>
       </c>
       <c r="M3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N3">
         <v>4</v>
@@ -749,10 +761,10 @@
         </is>
       </c>
       <c r="M6">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O6" s="3"/>
     </row>
@@ -1074,10 +1086,10 @@
         </is>
       </c>
       <c r="M11">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="N11">
-        <v>108</v>
+        <v>50</v>
       </c>
       <c r="O11" s="3"/>
     </row>
@@ -1138,6 +1150,12 @@
           <t xml:space="preserve">вневременная</t>
         </is>
       </c>
+      <c r="M12">
+        <v>458</v>
+      </c>
+      <c r="N12">
+        <v>194</v>
+      </c>
       <c r="O12" s="3"/>
     </row>
     <row r="13">
@@ -1197,6 +1215,12 @@
           <t xml:space="preserve">вневременная</t>
         </is>
       </c>
+      <c r="M13">
+        <v>1144</v>
+      </c>
+      <c r="N13">
+        <v>459</v>
+      </c>
       <c r="O13" s="3"/>
     </row>
     <row r="14">
@@ -1256,6 +1280,12 @@
           <t xml:space="preserve">вневременная</t>
         </is>
       </c>
+      <c r="M14">
+        <v>1970</v>
+      </c>
+      <c r="N14">
+        <v>664</v>
+      </c>
       <c r="O14" s="3"/>
     </row>
     <row r="15">
@@ -1446,7 +1476,7 @@
         </is>
       </c>
       <c r="M17">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="N17">
         <v>100</v>
@@ -1941,11 +1971,11 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сжечь 100 ресурсов неудачными попытками</t>
+          <t xml:space="preserve">Сжечь 250 ресурсов неудачными попытками</t>
         </is>
       </c>
       <c r="H25">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1962,14 +1992,14 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t xml:space="preserve">редкая</t>
+          <t xml:space="preserve">уникальная</t>
         </is>
       </c>
       <c r="M25">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="N25">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O25" s="3"/>
     </row>
@@ -2356,7 +2386,7 @@
         </is>
       </c>
       <c r="M31">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N31">
         <v>4</v>
@@ -2604,10 +2634,10 @@
         </is>
       </c>
       <c r="M35">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="N35">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="O35" s="3"/>
     </row>
@@ -2799,7 +2829,7 @@
         </is>
       </c>
       <c r="M38">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N38">
         <v>8</v>
@@ -2929,7 +2959,7 @@
         </is>
       </c>
       <c r="M40">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N40">
         <v>45</v>
@@ -3059,7 +3089,7 @@
         </is>
       </c>
       <c r="M42">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N42">
         <v>7</v>
@@ -3578,6 +3608,12 @@
           <t xml:space="preserve">вневременная</t>
         </is>
       </c>
+      <c r="M50">
+        <v>1144</v>
+      </c>
+      <c r="N50">
+        <v>459</v>
+      </c>
       <c r="O50" s="3"/>
     </row>
     <row r="51">
@@ -3873,11 +3909,11 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Продать на рынке 25 лотов</t>
+          <t xml:space="preserve">Продать на рынке 12 лотов</t>
         </is>
       </c>
       <c r="H55">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3894,14 +3930,14 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t xml:space="preserve">уникальная</t>
+          <t xml:space="preserve">редкая</t>
         </is>
       </c>
       <c r="M55">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="N55">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O55" s="3"/>
     </row>
@@ -4158,7 +4194,7 @@
         </is>
       </c>
       <c r="M59">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N59">
         <v>11</v>
@@ -4219,14 +4255,14 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t xml:space="preserve">эпическая</t>
+          <t xml:space="preserve">древняя</t>
         </is>
       </c>
       <c r="M60">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="N60">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="O60" s="3"/>
     </row>
@@ -4288,10 +4324,10 @@
         </is>
       </c>
       <c r="M61">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="N61">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="O61" s="3"/>
     </row>
@@ -4352,6 +4388,12 @@
           <t xml:space="preserve">вневременная</t>
         </is>
       </c>
+      <c r="M62">
+        <v>458</v>
+      </c>
+      <c r="N62">
+        <v>194</v>
+      </c>
       <c r="O62" s="3"/>
     </row>
     <row r="63">
@@ -4408,14 +4450,14 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t xml:space="preserve">редкая</t>
+          <t xml:space="preserve">уникальная</t>
         </is>
       </c>
       <c r="M63">
+        <v>10</v>
+      </c>
+      <c r="N63">
         <v>6</v>
-      </c>
-      <c r="N63">
-        <v>4</v>
       </c>
       <c r="O63" s="3"/>
     </row>
@@ -4477,10 +4519,10 @@
         </is>
       </c>
       <c r="M64">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="N64">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O64" s="3"/>
     </row>
@@ -4538,14 +4580,14 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t xml:space="preserve">эпическая</t>
+          <t xml:space="preserve">первородная</t>
         </is>
       </c>
       <c r="M65">
-        <v>41</v>
+        <v>99</v>
       </c>
       <c r="N65">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="O65" s="3"/>
     </row>
@@ -4606,6 +4648,12 @@
           <t xml:space="preserve">вневременная</t>
         </is>
       </c>
+      <c r="M66">
+        <v>1150</v>
+      </c>
+      <c r="N66">
+        <v>465</v>
+      </c>
       <c r="O66" s="3"/>
     </row>
     <row r="67">
@@ -4799,7 +4847,7 @@
         <v>36</v>
       </c>
       <c r="N69">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O69" s="3"/>
     </row>
@@ -4926,7 +4974,7 @@
         </is>
       </c>
       <c r="M71">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N71">
         <v>33</v>
@@ -4991,7 +5039,7 @@
         </is>
       </c>
       <c r="M72">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="N72">
         <v>82</v>
@@ -5121,7 +5169,7 @@
         </is>
       </c>
       <c r="M74">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N74">
         <v>66</v>
@@ -5511,10 +5559,10 @@
         </is>
       </c>
       <c r="M80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O80" s="3"/>
     </row>
@@ -5572,14 +5620,14 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t xml:space="preserve">уникальная</t>
+          <t xml:space="preserve">редкая</t>
         </is>
       </c>
       <c r="M81">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="N81">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O81" s="3"/>
     </row>
@@ -6945,7 +6993,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Создать призыв пробуждённого босса — Забытого</t>
+          <t xml:space="preserve">Создать призыв пробуждённого босса</t>
         </is>
       </c>
       <c r="H100">
@@ -7208,8 +7256,8473 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b3-cb-1</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эхо</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b3-cb</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/1</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные · III</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Победить 10 призванных врагов силы III</t>
+        </is>
+      </c>
+      <c r="H104">
+        <v>10</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Победы над призванными врагами силы III</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные враги</t>
+        </is>
+      </c>
+      <c r="K104">
+        <v>1</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">уникальная</t>
+        </is>
+      </c>
+      <c r="M104">
+        <v>39</v>
+      </c>
+      <c r="N104">
+        <v>21</v>
+      </c>
+      <c r="O104" s="3"/>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">III</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b3-rec-1</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ремесло</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b3-rec</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/1</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Книга цикла · III</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Найти 10 рецептов цикла III</t>
+        </is>
+      </c>
+      <c r="H105">
+        <v>10</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рецепты цикла III в книге</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Вторая находка места</t>
+        </is>
+      </c>
+      <c r="K105">
+        <v>1</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">эпическая</t>
+        </is>
+      </c>
+      <c r="M105">
+        <v>50</v>
+      </c>
+      <c r="N105">
+        <v>32</v>
+      </c>
+      <c r="O105" s="3"/>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">III</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b3-eq-1</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Странник</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b3-eq</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/1</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Арсенал цикла · III</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Получить 100 предметов снаряжения цикла III</t>
+        </is>
+      </c>
+      <c r="H106">
+        <v>100</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Предметы снаряжения цикла III</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Перековка</t>
+        </is>
+      </c>
+      <c r="K106">
+        <v>1</v>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">эпическая</t>
+        </is>
+      </c>
+      <c r="M106">
+        <v>66</v>
+      </c>
+      <c r="O106" s="3"/>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">III</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b3-tal-1</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Возрождённые</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рабочие и талисманы</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b3-tal</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/1</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Черты цикла · III</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Получить 100 духовных талисманов в цикле III</t>
+        </is>
+      </c>
+      <c r="H107">
+        <v>100</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Духовные талисманы, полученные в цикле III</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рабочие</t>
+        </is>
+      </c>
+      <c r="K107">
+        <v>1</v>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">древняя</t>
+        </is>
+      </c>
+      <c r="M107">
+        <v>87</v>
+      </c>
+      <c r="O107" s="3"/>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">III</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b3-m1</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Таинственные</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Неделя</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b3-m1</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/1</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пять верхушек</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">За одну неделю взять верх своей полосы в пяти режимах</t>
+        </is>
+      </c>
+      <c r="H108">
+        <v>1</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b3FiveTops</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Прах душ</t>
+        </is>
+      </c>
+      <c r="K108">
+        <v>2</v>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="O108" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Неделя, когда всё сошлось.</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">III</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">III</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b3-m2</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Таинственные</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эхо</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b3-m2</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/1</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сон окончен</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Победить Пробуждённого, призванного из мастерской</t>
+        </is>
+      </c>
+      <c r="H109">
+        <v>1</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b3AwakeKill</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные враги</t>
+        </is>
+      </c>
+      <c r="K109">
+        <v>2</v>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">древняя</t>
+        </is>
+      </c>
+      <c r="M109">
+        <v>72</v>
+      </c>
+      <c r="N109">
+        <v>34</v>
+      </c>
+      <c r="O109" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Разбуженное не засыпает само.</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">III</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">III</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b3-m3</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Таинственные</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ремесло</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b3-m3</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/1</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Двойная находка</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Получить две находки за один забег в крафтовое место цикла III</t>
+        </is>
+      </c>
+      <c r="H110">
+        <v>1</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b3TwoFinds</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Вторая находка места</t>
+        </is>
+      </c>
+      <c r="K110">
+        <v>1</v>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">уникальная</t>
+        </is>
+      </c>
+      <c r="M110">
+        <v>17</v>
+      </c>
+      <c r="N110">
+        <v>16</v>
+      </c>
+      <c r="O110" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Удача редко приходит одна.</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">III</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">III</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b3-m4</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Таинственные</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эхо</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b3-m4</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/1</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Вчерашние герои</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Победить призванного врага силы III отрядом из героев цикла II</t>
+        </is>
+      </c>
+      <c r="H111">
+        <v>1</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b3OldSquad</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные враги</t>
+        </is>
+      </c>
+      <c r="K111">
+        <v>1</v>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">эпическая</t>
+        </is>
+      </c>
+      <c r="M111">
+        <v>34</v>
+      </c>
+      <c r="N111">
+        <v>22</v>
+      </c>
+      <c r="O111" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Старая гвардия ещё держит строй.</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">III</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">III</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b3-m5</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Таинственные</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Странник</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b3-m5</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/1</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Во всеоружии</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Занять у одного героя все девять мест снаряжением цикла III</t>
+        </is>
+      </c>
+      <c r="H112">
+        <v>1</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b3FullSet</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Перековка</t>
+        </is>
+      </c>
+      <c r="K112">
+        <v>1</v>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">эпическая</t>
+        </is>
+      </c>
+      <c r="M112">
+        <v>44</v>
+      </c>
+      <c r="N112">
+        <v>26</v>
+      </c>
+      <c r="O112" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">С головы до пят.</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">III</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">III</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-cb-1</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эхо</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-cb</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/1</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные · IV</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Победить 75 призванных врагов силы IV</t>
+        </is>
+      </c>
+      <c r="H113">
+        <v>75</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Победы над призванными врагами силы IV</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные враги</t>
+        </is>
+      </c>
+      <c r="K113">
+        <v>1</v>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">древняя</t>
+        </is>
+      </c>
+      <c r="M113">
+        <v>273</v>
+      </c>
+      <c r="N113">
+        <v>111</v>
+      </c>
+      <c r="O113" s="3"/>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-aw-1</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эхо</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-aw</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/2</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пробуждённые · IV · 1</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Победить 2 Пробуждённых в цикле IV</t>
+        </is>
+      </c>
+      <c r="H114">
+        <v>2</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Победы над Пробуждёнными в цикле IV</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные враги</t>
+        </is>
+      </c>
+      <c r="K114">
+        <v>1</v>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">древняя</t>
+        </is>
+      </c>
+      <c r="M114">
+        <v>307</v>
+      </c>
+      <c r="N114">
+        <v>137</v>
+      </c>
+      <c r="O114" s="3"/>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-aw-2</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эхо</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-aw</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2/2</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пробуждённые · IV · 2</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Победить 3 Пробуждённых в цикле IV</t>
+        </is>
+      </c>
+      <c r="H115">
+        <v>3</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Победы над Пробуждёнными в цикле IV</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные враги</t>
+        </is>
+      </c>
+      <c r="K115">
+        <v>1</v>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">первородная</t>
+        </is>
+      </c>
+      <c r="M115">
+        <v>407</v>
+      </c>
+      <c r="N115">
+        <v>181</v>
+      </c>
+      <c r="O115" s="3"/>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-run-1</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ремесло</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-run</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/2</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Места ремесла · IV · 1</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пройти крафтовые места цикла IV 2 000 раз</t>
+        </is>
+      </c>
+      <c r="H116">
+        <v>2000</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Забеги в крафтовые места цикла IV</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ресурс крафтового места</t>
+        </is>
+      </c>
+      <c r="K116">
+        <v>1</v>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">древняя</t>
+        </is>
+      </c>
+      <c r="M116">
+        <v>254</v>
+      </c>
+      <c r="N116">
+        <v>105</v>
+      </c>
+      <c r="O116" s="3"/>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-run-2</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ремесло</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-run</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2/2</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Места ремесла · IV · 2</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пройти крафтовые места цикла IV 2 500 раз</t>
+        </is>
+      </c>
+      <c r="H117">
+        <v>2500</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Забеги в крафтовые места цикла IV</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ресурс крафтового места</t>
+        </is>
+      </c>
+      <c r="K117">
+        <v>1</v>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">древняя</t>
+        </is>
+      </c>
+      <c r="M117">
+        <v>291</v>
+      </c>
+      <c r="N117">
+        <v>119</v>
+      </c>
+      <c r="O117" s="3"/>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-rec-1</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ремесло</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-rec</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/3</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Книга цикла · IV · 1</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Найти 75 рецептов цикла IV</t>
+        </is>
+      </c>
+      <c r="H118">
+        <v>75</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рецепты цикла IV в книге</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Вторая находка места</t>
+        </is>
+      </c>
+      <c r="K118">
+        <v>1</v>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">первородная</t>
+        </is>
+      </c>
+      <c r="M118">
+        <v>373</v>
+      </c>
+      <c r="N118">
+        <v>181</v>
+      </c>
+      <c r="O118" s="3"/>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-rec-2</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ремесло</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-rec</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2/3</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Книга цикла · IV · 2</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Найти 80 рецептов цикла IV</t>
+        </is>
+      </c>
+      <c r="H119">
+        <v>80</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рецепты цикла IV в книге</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Вторая находка места</t>
+        </is>
+      </c>
+      <c r="K119">
+        <v>1</v>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">первородная</t>
+        </is>
+      </c>
+      <c r="M119">
+        <v>391</v>
+      </c>
+      <c r="N119">
+        <v>190</v>
+      </c>
+      <c r="O119" s="3"/>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-rec-3</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ремесло</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-rec</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/3</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Книга цикла · IV · 3</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Найти 90 рецептов цикла IV</t>
+        </is>
+      </c>
+      <c r="H120">
+        <v>90</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рецепты цикла IV в книге</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Вторая находка места</t>
+        </is>
+      </c>
+      <c r="K120">
+        <v>1</v>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">первородная</t>
+        </is>
+      </c>
+      <c r="M120">
+        <v>427</v>
+      </c>
+      <c r="O120" s="3"/>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-circ-1</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Неделя</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-circ</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/3</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Круг за кругом · IV · 1</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Закрыть с кланом 100 кругов кланового босса в цикле IV</t>
+        </is>
+      </c>
+      <c r="H121">
+        <v>100</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Круги кланового босса, закрытые кланом в цикле IV</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ритуалы</t>
+        </is>
+      </c>
+      <c r="K121">
+        <v>1</v>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">эпическая</t>
+        </is>
+      </c>
+      <c r="M121">
+        <v>193</v>
+      </c>
+      <c r="N121">
+        <v>166</v>
+      </c>
+      <c r="O121" s="3"/>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-circ-2</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Неделя</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-circ</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2/3</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Круг за кругом · IV · 2</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Закрыть с кланом 150 кругов кланового босса в цикле IV</t>
+        </is>
+      </c>
+      <c r="H122">
+        <v>150</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Круги кланового босса, закрытые кланом в цикле IV</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ритуалы</t>
+        </is>
+      </c>
+      <c r="K122">
+        <v>1</v>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">древняя</t>
+        </is>
+      </c>
+      <c r="M122">
+        <v>237</v>
+      </c>
+      <c r="O122" s="3"/>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-circ-3</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Неделя</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-circ</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/3</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Круг за кругом · IV · 3</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Закрыть с кланом 250 кругов кланового босса в цикле IV</t>
+        </is>
+      </c>
+      <c r="H123">
+        <v>250</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Круги кланового босса, закрытые кланом в цикле IV</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Календарь</t>
+        </is>
+      </c>
+      <c r="K123">
+        <v>1</v>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">древняя</t>
+        </is>
+      </c>
+      <c r="M123">
+        <v>324</v>
+      </c>
+      <c r="O123" s="3"/>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-step-1</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Неделя</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-step</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/2</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ступень за ступенью · IV · 1</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Взять в недельных режимах 350 ступеней полосы цикла IV</t>
+        </is>
+      </c>
+      <c r="H124">
+        <v>350</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ступени полосы цикла IV, взятые в недельных режимах</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Календарь</t>
+        </is>
+      </c>
+      <c r="K124">
+        <v>1</v>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">эпическая</t>
+        </is>
+      </c>
+      <c r="M124">
+        <v>222</v>
+      </c>
+      <c r="N124">
+        <v>134</v>
+      </c>
+      <c r="O124" s="3"/>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-step-2</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Неделя</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-step</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2/2</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ступень за ступенью · IV · 2</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Взять в недельных режимах 750 ступеней полосы цикла IV</t>
+        </is>
+      </c>
+      <c r="H125">
+        <v>750</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ступени полосы цикла IV, взятые в недельных режимах</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Календарь</t>
+        </is>
+      </c>
+      <c r="K125">
+        <v>1</v>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">первородная</t>
+        </is>
+      </c>
+      <c r="M125">
+        <v>355</v>
+      </c>
+      <c r="O125" s="3"/>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-tal-1</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Возрождённые</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рабочие и талисманы</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-tal</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/1</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Черты цикла · IV</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Получить 100 духовных талисманов в цикле IV</t>
+        </is>
+      </c>
+      <c r="H126">
+        <v>100</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Духовные талисманы, полученные в цикле IV</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рабочие</t>
+        </is>
+      </c>
+      <c r="K126">
+        <v>1</v>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">эпическая</t>
+        </is>
+      </c>
+      <c r="M126">
+        <v>154</v>
+      </c>
+      <c r="N126">
+        <v>79</v>
+      </c>
+      <c r="O126" s="3"/>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-eh-1</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Возрождённые</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Герои</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-eh</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/3</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Герои нашествий · IV · 1</t>
+        </is>
+      </c>
+      <c r="G127" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Собрать 3 героев Эхо цикла IV</t>
+        </is>
+      </c>
+      <c r="H127">
+        <v>3</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Герои Эхо цикла IV, собранные из осколков</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Прах душ</t>
+        </is>
+      </c>
+      <c r="K127">
+        <v>1</v>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">эпическая</t>
+        </is>
+      </c>
+      <c r="M127">
+        <v>139</v>
+      </c>
+      <c r="N127">
+        <v>68</v>
+      </c>
+      <c r="O127" s="3"/>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-eh-2</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Возрождённые</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Герои</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-eh</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2/3</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Герои нашествий · IV · 2</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Собрать 6 героев Эхо цикла IV</t>
+        </is>
+      </c>
+      <c r="H128">
+        <v>6</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Герои Эхо цикла IV, собранные из осколков</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Прах душ</t>
+        </is>
+      </c>
+      <c r="K128">
+        <v>1</v>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">эпическая</t>
+        </is>
+      </c>
+      <c r="M128">
+        <v>173</v>
+      </c>
+      <c r="N128">
+        <v>86</v>
+      </c>
+      <c r="O128" s="3"/>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-eh-3</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Возрождённые</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Герои</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-eh</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/3</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Герои нашествий · IV · 3</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Собрать 9 героев Эхо цикла IV</t>
+        </is>
+      </c>
+      <c r="H129">
+        <v>9</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Герои Эхо цикла IV, собранные из осколков</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Прах душ</t>
+        </is>
+      </c>
+      <c r="K129">
+        <v>1</v>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">эпическая</t>
+        </is>
+      </c>
+      <c r="M129">
+        <v>206</v>
+      </c>
+      <c r="N129">
+        <v>104</v>
+      </c>
+      <c r="O129" s="3"/>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-lim-1</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Возрождённые</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Главы, ордены, пределы</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-lim</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/2</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Третий предел · IV</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пробить третий рунный предел всем пятерым героям отряда цикла IV</t>
+        </is>
+      </c>
+      <c r="H130">
+        <v>3</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рунный предел, пробитый у всех пятерых героев отряда цикла IV</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рунный ключ</t>
+        </is>
+      </c>
+      <c r="K130">
+        <v>1</v>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">эпическая</t>
+        </is>
+      </c>
+      <c r="M130">
+        <v>135</v>
+      </c>
+      <c r="N130">
+        <v>69</v>
+      </c>
+      <c r="O130" s="3"/>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-lim-2</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Возрождённые</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Главы, ордены, пределы</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-lim</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2/2</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пятый предел · IV</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пробить пятый рунный предел всем пятерым героям отряда цикла IV</t>
+        </is>
+      </c>
+      <c r="H131">
+        <v>5</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рунный предел, пробитый у всех пятерых героев отряда цикла IV</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рунный ключ</t>
+        </is>
+      </c>
+      <c r="K131">
+        <v>1</v>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">древняя</t>
+        </is>
+      </c>
+      <c r="M131">
+        <v>337</v>
+      </c>
+      <c r="N131">
+        <v>147</v>
+      </c>
+      <c r="O131" s="3"/>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-recAll-1</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ремесло</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-recAll</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/1</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Вся книга цикла · IV</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Найти все рецепты цикла IV</t>
+        </is>
+      </c>
+      <c r="H132">
+        <v>94</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рецепты цикла IV в книге</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Уникальный ресурс</t>
+        </is>
+      </c>
+      <c r="K132">
+        <v>1</v>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">первородная</t>
+        </is>
+      </c>
+      <c r="M132">
+        <v>441</v>
+      </c>
+      <c r="O132" s="3"/>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-top-1</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Неделя</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-top</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/2</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Верх полосы · IV</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Взять верх полосы цикла IV в недельном режиме</t>
+        </is>
+      </c>
+      <c r="H133">
+        <v>1</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Недельные режимы, где взят верх полосы цикла IV</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Базовые ресурсы</t>
+        </is>
+      </c>
+      <c r="K133">
+        <v>1</v>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="N133">
+        <v>56</v>
+      </c>
+      <c r="O133" s="3"/>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-top-2</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Неделя</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-top</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2/2</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Три вершины · IV</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Взять верх полосы цикла IV в трёх недельных режимах</t>
+        </is>
+      </c>
+      <c r="H134">
+        <v>3</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Недельные режимы, где взят верх полосы цикла IV</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Уникальный ресурс</t>
+        </is>
+      </c>
+      <c r="K134">
+        <v>1</v>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="N134">
+        <v>56</v>
+      </c>
+      <c r="O134" s="3"/>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-m1</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Таинственные</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Герои</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-m1</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/1</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Чужая неделя</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Собрать героя Эхо, влив в него прах Эха в неделю другой расы</t>
+        </is>
+      </c>
+      <c r="H135">
+        <v>1</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4OtherWeek</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Прах душ</t>
+        </is>
+      </c>
+      <c r="K135">
+        <v>1</v>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">эпическая</t>
+        </is>
+      </c>
+      <c r="M135">
+        <v>145</v>
+      </c>
+      <c r="N135">
+        <v>61</v>
+      </c>
+      <c r="O135" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Долги отдают не по расписанию.</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-m2</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Таинственные</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Неделя</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-m2</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/1</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Точка в споре</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Добить кланового босса своей атакой</t>
+        </is>
+      </c>
+      <c r="H136">
+        <v>1</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4LastHit</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ритуалы</t>
+        </is>
+      </c>
+      <c r="K136">
+        <v>1</v>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">эпическая</t>
+        </is>
+      </c>
+      <c r="M136">
+        <v>120</v>
+      </c>
+      <c r="N136">
+        <v>54</v>
+      </c>
+      <c r="O136" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Последнее слово — за тобой.</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-m3</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Таинственные</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эхо</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-m3</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/1</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Без потерь</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Победить призванного врага силы IV, не потеряв ни одного героя</t>
+        </is>
+      </c>
+      <c r="H137">
+        <v>1</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4NoLoss</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные враги</t>
+        </is>
+      </c>
+      <c r="K137">
+        <v>1</v>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">эпическая</t>
+        </is>
+      </c>
+      <c r="M137">
+        <v>117</v>
+      </c>
+      <c r="N137">
+        <v>53</v>
+      </c>
+      <c r="O137" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Вернулись все, кто вышел.</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-m4</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Таинственные</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Неделя</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-m4</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/1</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Как есть</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Исполнить все контракты недели, ни разу не заменив задание</t>
+        </is>
+      </c>
+      <c r="H138">
+        <v>1</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4NoSwap</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Календарь</t>
+        </is>
+      </c>
+      <c r="K138">
+        <v>1</v>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">древняя</t>
+        </is>
+      </c>
+      <c r="M138">
+        <v>135</v>
+      </c>
+      <c r="N138">
+        <v>57</v>
+      </c>
+      <c r="O138" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Что дали, то и сделал.</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-m5</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Таинственные</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эхо</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4-m5</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/1</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Двое за день</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Победить двух призванных врагов за один день</t>
+        </is>
+      </c>
+      <c r="H139">
+        <v>1</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4TwoADay</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Уникальный ресурс</t>
+        </is>
+      </c>
+      <c r="K139">
+        <v>1</v>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">древняя</t>
+        </is>
+      </c>
+      <c r="M139">
+        <v>165</v>
+      </c>
+      <c r="N139">
+        <v>55</v>
+      </c>
+      <c r="O139" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">День на двоих.</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-cb-1</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эхо</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-cb</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/3</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные · V · 1</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Победить 25 призванных врагов силы V</t>
+        </is>
+      </c>
+      <c r="H140">
+        <v>25</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Победы над призванными врагами силы V</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные враги</t>
+        </is>
+      </c>
+      <c r="K140">
+        <v>1</v>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">древняя</t>
+        </is>
+      </c>
+      <c r="M140">
+        <v>507</v>
+      </c>
+      <c r="N140">
+        <v>212</v>
+      </c>
+      <c r="O140" s="3"/>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-cb-2</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эхо</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-cb</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2/3</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные · V · 2</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Победить 200 призванных врагов силы V</t>
+        </is>
+      </c>
+      <c r="H141">
+        <v>200</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Победы над призванными врагами силы V</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные враги</t>
+        </is>
+      </c>
+      <c r="K141">
+        <v>1</v>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">первородная</t>
+        </is>
+      </c>
+      <c r="M141">
+        <v>857</v>
+      </c>
+      <c r="N141">
+        <v>344</v>
+      </c>
+      <c r="O141" s="3"/>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-cb-3</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эхо</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-cb</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/3</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные · V · 3</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Победить 280 призванных врагов силы V</t>
+        </is>
+      </c>
+      <c r="H142">
+        <v>280</v>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Победы над призванными врагами силы V</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные враги</t>
+        </is>
+      </c>
+      <c r="K142">
+        <v>1</v>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="M142">
+        <v>1017</v>
+      </c>
+      <c r="N142">
+        <v>404</v>
+      </c>
+      <c r="O142" s="3"/>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-aw-1</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эхо</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-aw</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/2</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пробуждённые · V · 1</t>
+        </is>
+      </c>
+      <c r="G143" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Победить 3 Пробуждённых в цикле V</t>
+        </is>
+      </c>
+      <c r="H143">
+        <v>3</v>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Победы над Пробуждёнными в цикле V</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные враги</t>
+        </is>
+      </c>
+      <c r="K143">
+        <v>1</v>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">первородная</t>
+        </is>
+      </c>
+      <c r="M143">
+        <v>766</v>
+      </c>
+      <c r="N143">
+        <v>328</v>
+      </c>
+      <c r="O143" s="3"/>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-aw-2</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эхо</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-aw</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2/2</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пробуждённые · V · 2</t>
+        </is>
+      </c>
+      <c r="G144" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Победить 5 Пробуждённых в цикле V</t>
+        </is>
+      </c>
+      <c r="H144">
+        <v>5</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Победы над Пробуждёнными в цикле V</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные враги</t>
+        </is>
+      </c>
+      <c r="K144">
+        <v>1</v>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="M144">
+        <v>972</v>
+      </c>
+      <c r="N144">
+        <v>418</v>
+      </c>
+      <c r="O144" s="3"/>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-run-1</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ремесло</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-run</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/3</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Места ремесла · V · 1</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пройти крафтовые места цикла V 2 500 раз</t>
+        </is>
+      </c>
+      <c r="H145">
+        <v>2500</v>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Забеги в крафтовые места цикла V</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ресурс крафтового места</t>
+        </is>
+      </c>
+      <c r="K145">
+        <v>1</v>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">древняя</t>
+        </is>
+      </c>
+      <c r="M145">
+        <v>606</v>
+      </c>
+      <c r="N145">
+        <v>249</v>
+      </c>
+      <c r="O145" s="3"/>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-run-2</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ремесло</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-run</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2/3</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Места ремесла · V · 2</t>
+        </is>
+      </c>
+      <c r="G146" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пройти крафтовые места цикла V 4 000 раз</t>
+        </is>
+      </c>
+      <c r="H146">
+        <v>4000</v>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Забеги в крафтовые места цикла V</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ресурс крафтового места</t>
+        </is>
+      </c>
+      <c r="K146">
+        <v>1</v>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">первородная</t>
+        </is>
+      </c>
+      <c r="M146">
+        <v>695</v>
+      </c>
+      <c r="N146">
+        <v>282</v>
+      </c>
+      <c r="O146" s="3"/>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-run-3</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ремесло</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-run</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/3</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Места ремесла · V · 3</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пройти крафтовые места цикла V 7 500 раз</t>
+        </is>
+      </c>
+      <c r="H147">
+        <v>7500</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Забеги в крафтовые места цикла V</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ресурс крафтового места</t>
+        </is>
+      </c>
+      <c r="K147">
+        <v>1</v>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">первородная</t>
+        </is>
+      </c>
+      <c r="M147">
+        <v>902</v>
+      </c>
+      <c r="N147">
+        <v>360</v>
+      </c>
+      <c r="O147" s="3"/>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-rec-1</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ремесло</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-rec</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/1</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Книга цикла · V</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Найти 80 рецептов цикла V</t>
+        </is>
+      </c>
+      <c r="H148">
+        <v>80</v>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рецепты цикла V в книге</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Вторая находка места</t>
+        </is>
+      </c>
+      <c r="K148">
+        <v>1</v>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">первородная</t>
+        </is>
+      </c>
+      <c r="M148">
+        <v>743</v>
+      </c>
+      <c r="N148">
+        <v>334</v>
+      </c>
+      <c r="O148" s="3"/>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-circ-1</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Неделя</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-circ</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/1</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Круг за кругом · V</t>
+        </is>
+      </c>
+      <c r="G149" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Закрыть с кланом 200 кругов кланового босса в цикле V</t>
+        </is>
+      </c>
+      <c r="H149">
+        <v>200</v>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Круги кланового босса, закрытые кланом в цикле V</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ритуалы</t>
+        </is>
+      </c>
+      <c r="K149">
+        <v>1</v>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">древняя</t>
+        </is>
+      </c>
+      <c r="M149">
+        <v>657</v>
+      </c>
+      <c r="N149">
+        <v>427</v>
+      </c>
+      <c r="O149" s="3"/>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-step-1</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Неделя</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-step</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/4</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ступень за ступенью · V · 1</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Взять в недельных режимах 250 ступеней полосы цикла V</t>
+        </is>
+      </c>
+      <c r="H150">
+        <v>250</v>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ступени полосы цикла V, взятые в недельных режимах</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Календарь</t>
+        </is>
+      </c>
+      <c r="K150">
+        <v>1</v>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">древняя</t>
+        </is>
+      </c>
+      <c r="M150">
+        <v>541</v>
+      </c>
+      <c r="N150">
+        <v>254</v>
+      </c>
+      <c r="O150" s="3"/>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-step-2</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Неделя</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-step</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2/4</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ступень за ступенью · V · 2</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Взять в недельных режимах 1 400 ступеней полосы цикла V</t>
+        </is>
+      </c>
+      <c r="H151">
+        <v>1400</v>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ступени полосы цикла V, взятые в недельных режимах</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Календарь</t>
+        </is>
+      </c>
+      <c r="K151">
+        <v>1</v>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="M151">
+        <v>924</v>
+      </c>
+      <c r="O151" s="3"/>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-step-3</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Неделя</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-step</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ступень за ступенью · V · 3</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Взять в недельных режимах 1 750 ступеней полосы цикла V</t>
+        </is>
+      </c>
+      <c r="H152">
+        <v>1750</v>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ступени полосы цикла V, взятые в недельных режимах</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Календарь</t>
+        </is>
+      </c>
+      <c r="K152">
+        <v>1</v>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="M152">
+        <v>1041</v>
+      </c>
+      <c r="O152" s="3"/>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-step-4</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Неделя</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-step</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ступень за ступенью · V · 4</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Взять в недельных режимах 2 000 ступеней полосы цикла V</t>
+        </is>
+      </c>
+      <c r="H153">
+        <v>2000</v>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ступени полосы цикла V, взятые в недельных режимах</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Календарь</t>
+        </is>
+      </c>
+      <c r="K153">
+        <v>1</v>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="M153">
+        <v>1124</v>
+      </c>
+      <c r="O153" s="3"/>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-eq-1</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Странник</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-eq</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/3</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Арсенал цикла · V · 1</t>
+        </is>
+      </c>
+      <c r="G154" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Получить 300 предметов снаряжения цикла V</t>
+        </is>
+      </c>
+      <c r="H154">
+        <v>300</v>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Предметы снаряжения цикла V</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Перековка</t>
+        </is>
+      </c>
+      <c r="K154">
+        <v>1</v>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">древняя</t>
+        </is>
+      </c>
+      <c r="M154">
+        <v>582</v>
+      </c>
+      <c r="N154">
+        <v>291</v>
+      </c>
+      <c r="O154" s="3"/>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-eq-2</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Странник</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-eq</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2/3</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Арсенал цикла · V · 2</t>
+        </is>
+      </c>
+      <c r="G155" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Получить 1 000 предметов снаряжения цикла V</t>
+        </is>
+      </c>
+      <c r="H155">
+        <v>1000</v>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Предметы снаряжения цикла V</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Перековка</t>
+        </is>
+      </c>
+      <c r="K155">
+        <v>1</v>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">первородная</t>
+        </is>
+      </c>
+      <c r="M155">
+        <v>874</v>
+      </c>
+      <c r="O155" s="3"/>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-eq-3</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Странник</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-eq</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/3</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Арсенал цикла · V · 3</t>
+        </is>
+      </c>
+      <c r="G156" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Получить 1 500 предметов снаряжения цикла V</t>
+        </is>
+      </c>
+      <c r="H156">
+        <v>1500</v>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Предметы снаряжения цикла V</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Перековка</t>
+        </is>
+      </c>
+      <c r="K156">
+        <v>1</v>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="M156">
+        <v>1082</v>
+      </c>
+      <c r="O156" s="3"/>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-tal-1</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Возрождённые</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рабочие и талисманы</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-tal</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/3</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Черты цикла · V · 1</t>
+        </is>
+      </c>
+      <c r="G157" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Получить 200 духовных талисманов в цикле V</t>
+        </is>
+      </c>
+      <c r="H157">
+        <v>200</v>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Духовные талисманы, полученные в цикле V</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рабочие</t>
+        </is>
+      </c>
+      <c r="K157">
+        <v>1</v>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">древняя</t>
+        </is>
+      </c>
+      <c r="M157">
+        <v>630</v>
+      </c>
+      <c r="N157">
+        <v>297</v>
+      </c>
+      <c r="O157" s="3"/>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-tal-2</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Возрождённые</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рабочие и талисманы</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-tal</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2/3</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Черты цикла · V · 2</t>
+        </is>
+      </c>
+      <c r="G158" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Получить 300 духовных талисманов в цикле V</t>
+        </is>
+      </c>
+      <c r="H158">
+        <v>300</v>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Духовные талисманы, полученные в цикле V</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рабочие</t>
+        </is>
+      </c>
+      <c r="K158">
+        <v>1</v>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">первородная</t>
+        </is>
+      </c>
+      <c r="M158">
+        <v>717</v>
+      </c>
+      <c r="N158">
+        <v>349</v>
+      </c>
+      <c r="O158" s="3"/>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-tal-3</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Возрождённые</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рабочие и талисманы</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-tal</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/3</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Черты цикла · V · 3</t>
+        </is>
+      </c>
+      <c r="G159" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Получить 750 духовных талисманов в цикле V</t>
+        </is>
+      </c>
+      <c r="H159">
+        <v>750</v>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Духовные талисманы, полученные в цикле V</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рабочие</t>
+        </is>
+      </c>
+      <c r="K159">
+        <v>1</v>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="M159">
+        <v>1106</v>
+      </c>
+      <c r="O159" s="3"/>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-val-1</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Возрождённые</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Главы, ордены, пределы</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-val</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/5</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Доблесть цикла · V · 1</t>
+        </is>
+      </c>
+      <c r="G160" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Поднять доблесть героям цикла V 3 раза</t>
+        </is>
+      </c>
+      <c r="H160">
+        <v>3</v>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Доблесть героев цикла V: сколько раз поднята</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Уровни героев</t>
+        </is>
+      </c>
+      <c r="K160">
+        <v>1</v>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">первородная</t>
+        </is>
+      </c>
+      <c r="M160">
+        <v>792</v>
+      </c>
+      <c r="N160">
+        <v>323</v>
+      </c>
+      <c r="O160" s="3"/>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-val-2</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Возрождённые</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Главы, ордены, пределы</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-val</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2/5</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Доблесть цикла · V · 2</t>
+        </is>
+      </c>
+      <c r="G161" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Поднять доблесть героям цикла V 4 раза</t>
+        </is>
+      </c>
+      <c r="H161">
+        <v>4</v>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Доблесть героев цикла V: сколько раз поднята</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Дух за убийство</t>
+        </is>
+      </c>
+      <c r="K161">
+        <v>1</v>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">первородная</t>
+        </is>
+      </c>
+      <c r="M161">
+        <v>833</v>
+      </c>
+      <c r="N161">
+        <v>338</v>
+      </c>
+      <c r="O161" s="3"/>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-val-3</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Возрождённые</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Главы, ордены, пределы</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-val</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/5</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Доблесть цикла · V · 3</t>
+        </is>
+      </c>
+      <c r="G162" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Поднять доблесть героям цикла V 7 раз</t>
+        </is>
+      </c>
+      <c r="H162">
+        <v>7</v>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Доблесть героев цикла V: сколько раз поднята</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Дух за убийство</t>
+        </is>
+      </c>
+      <c r="K162">
+        <v>1</v>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="M162">
+        <v>951</v>
+      </c>
+      <c r="N162">
+        <v>384</v>
+      </c>
+      <c r="O162" s="3"/>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-val-4</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Возрождённые</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Главы, ордены, пределы</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-val</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/5</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Доблесть цикла · V · 4</t>
+        </is>
+      </c>
+      <c r="G163" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Поднять доблесть героям цикла V 8 раз</t>
+        </is>
+      </c>
+      <c r="H163">
+        <v>8</v>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Доблесть героев цикла V: сколько раз поднята</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Золото за убийство</t>
+        </is>
+      </c>
+      <c r="K163">
+        <v>1</v>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="M163">
+        <v>990</v>
+      </c>
+      <c r="N163">
+        <v>399</v>
+      </c>
+      <c r="O163" s="3"/>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-val-5</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Возрождённые</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Главы, ордены, пределы</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-val</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5/5</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Доблесть цикла · V · 5</t>
+        </is>
+      </c>
+      <c r="G164" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Поднять доблесть героям цикла V 10 раз</t>
+        </is>
+      </c>
+      <c r="H164">
+        <v>10</v>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Доблесть героев цикла V: сколько раз поднята</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Золото за убийство</t>
+        </is>
+      </c>
+      <c r="K164">
+        <v>1</v>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="M164">
+        <v>1067</v>
+      </c>
+      <c r="N164">
+        <v>429</v>
+      </c>
+      <c r="O164" s="3"/>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-eh-1</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Возрождённые</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Герои</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-eh</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/3</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Герои нашествий · V · 1</t>
+        </is>
+      </c>
+      <c r="G165" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Собрать 3 героев Эхо цикла V</t>
+        </is>
+      </c>
+      <c r="H165">
+        <v>3</v>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Герои Эхо цикла V, собранные из осколков</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Прах душ</t>
+        </is>
+      </c>
+      <c r="K165">
+        <v>1</v>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">древняя</t>
+        </is>
+      </c>
+      <c r="M165">
+        <v>491</v>
+      </c>
+      <c r="N165">
+        <v>212</v>
+      </c>
+      <c r="O165" s="3"/>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-eh-2</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Возрождённые</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Герои</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-eh</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2/3</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Герои нашествий · V · 2</t>
+        </is>
+      </c>
+      <c r="G166" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Собрать 6 героев Эхо цикла V</t>
+        </is>
+      </c>
+      <c r="H166">
+        <v>6</v>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Герои Эхо цикла V, собранные из осколков</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Прах душ</t>
+        </is>
+      </c>
+      <c r="K166">
+        <v>1</v>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">древняя</t>
+        </is>
+      </c>
+      <c r="M166">
+        <v>525</v>
+      </c>
+      <c r="N166">
+        <v>230</v>
+      </c>
+      <c r="O166" s="3"/>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-eh-3</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Возрождённые</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Герои</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-eh</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/3</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Герои нашествий · V · 3</t>
+        </is>
+      </c>
+      <c r="G167" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Собрать 9 героев Эхо цикла V</t>
+        </is>
+      </c>
+      <c r="H167">
+        <v>9</v>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Герои Эхо цикла V, собранные из осколков</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Прах душ</t>
+        </is>
+      </c>
+      <c r="K167">
+        <v>1</v>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">древняя</t>
+        </is>
+      </c>
+      <c r="M167">
+        <v>558</v>
+      </c>
+      <c r="N167">
+        <v>248</v>
+      </c>
+      <c r="O167" s="3"/>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-lim-1</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Возрождённые</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Главы, ордены, пределы</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-lim</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/2</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Третий предел · V</t>
+        </is>
+      </c>
+      <c r="G168" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пробить третий рунный предел всем пятерым героям отряда цикла V</t>
+        </is>
+      </c>
+      <c r="H168">
+        <v>3</v>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рунный предел, пробитый у всех пятерых героев отряда цикла V</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рунный ключ</t>
+        </is>
+      </c>
+      <c r="K168">
+        <v>1</v>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">древняя</t>
+        </is>
+      </c>
+      <c r="M168">
+        <v>485</v>
+      </c>
+      <c r="N168">
+        <v>213</v>
+      </c>
+      <c r="O168" s="3"/>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-lim-2</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Возрождённые</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Главы, ордены, пределы</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-lim</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2/2</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пятый предел · V</t>
+        </is>
+      </c>
+      <c r="G169" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пробить пятый рунный предел всем пятерым героям отряда цикла V</t>
+        </is>
+      </c>
+      <c r="H169">
+        <v>5</v>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рунный предел, пробитый у всех пятерых героев отряда цикла V</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рунный ключ</t>
+        </is>
+      </c>
+      <c r="K169">
+        <v>1</v>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">древняя</t>
+        </is>
+      </c>
+      <c r="M169">
+        <v>670</v>
+      </c>
+      <c r="N169">
+        <v>276</v>
+      </c>
+      <c r="O169" s="3"/>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-recAll-1</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ремесло</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-recAll</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/1</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Вся книга цикла · V</t>
+        </is>
+      </c>
+      <c r="G170" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Найти все рецепты цикла V</t>
+        </is>
+      </c>
+      <c r="H170">
+        <v>98</v>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рецепты цикла V в книге</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Уникальный ресурс</t>
+        </is>
+      </c>
+      <c r="K170">
+        <v>1</v>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">первородная</t>
+        </is>
+      </c>
+      <c r="M170">
+        <v>807</v>
+      </c>
+      <c r="N170">
+        <v>365</v>
+      </c>
+      <c r="O170" s="3"/>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-top-1</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Неделя</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-top</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/2</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Верх полосы · V</t>
+        </is>
+      </c>
+      <c r="G171" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Взять верх полосы цикла V в недельном режиме</t>
+        </is>
+      </c>
+      <c r="H171">
+        <v>1</v>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Недельные режимы, где взят верх полосы цикла V</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Базовые ресурсы</t>
+        </is>
+      </c>
+      <c r="K171">
+        <v>1</v>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="N171">
+        <v>200</v>
+      </c>
+      <c r="O171" s="3"/>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-top-2</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Неделя</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-top</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2/2</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Три вершины · V</t>
+        </is>
+      </c>
+      <c r="G172" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Взять верх полосы цикла V в трёх недельных режимах</t>
+        </is>
+      </c>
+      <c r="H172">
+        <v>3</v>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Недельные режимы, где взят верх полосы цикла V</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Уникальный ресурс</t>
+        </is>
+      </c>
+      <c r="K172">
+        <v>1</v>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="N172">
+        <v>200</v>
+      </c>
+      <c r="O172" s="3"/>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-m1</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Таинственные</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эхо</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-m1</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/1</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Без промаха</t>
+        </is>
+      </c>
+      <c r="G173" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Победить Пробуждённого с первой атаки</t>
+        </is>
+      </c>
+      <c r="H173">
+        <v>1</v>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5OneShot</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Вторая находка места</t>
+        </is>
+      </c>
+      <c r="K173">
+        <v>2</v>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">первородная</t>
+        </is>
+      </c>
+      <c r="M173">
+        <v>607</v>
+      </c>
+      <c r="N173">
+        <v>238</v>
+      </c>
+      <c r="O173" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Второй попытки не понадобилось.</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-m2</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Таинственные</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Неделя</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-m2</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/1</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Не отдать вершину</t>
+        </is>
+      </c>
+      <c r="G174" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Три недели подряд брать верх своей полосы в Эхо</t>
+        </is>
+      </c>
+      <c r="H174">
+        <v>1</v>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5HoldTop</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Базовые ресурсы</t>
+        </is>
+      </c>
+      <c r="K174">
+        <v>1</v>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="N174">
+        <v>214</v>
+      </c>
+      <c r="O174" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Высоту мало взять — её держат.</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-m3</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Таинственные</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Герои</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-m3</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/1</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">За одну неделю</t>
+        </is>
+      </c>
+      <c r="G175" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Собрать героя Эхо цикла V из осколков одной недели</t>
+        </is>
+      </c>
+      <c r="H175">
+        <v>1</v>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5WeekHero</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Прах душ</t>
+        </is>
+      </c>
+      <c r="K175">
+        <v>1</v>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="N175">
+        <v>253</v>
+      </c>
+      <c r="O175" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Семь дней — и он с тобой.</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-m4</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Таинственные</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Стражи и ключи</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-m4</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/1</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">На последнем делении</t>
+        </is>
+      </c>
+      <c r="G176" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Победить рунного стража цикла V в последнем раунде боя</t>
+        </is>
+      </c>
+      <c r="H176">
+        <v>1</v>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5LastTick</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рунный ключ</t>
+        </is>
+      </c>
+      <c r="K176">
+        <v>1</v>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">древняя</t>
+        </is>
+      </c>
+      <c r="M176">
+        <v>492</v>
+      </c>
+      <c r="N176">
+        <v>205</v>
+      </c>
+      <c r="O176" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Стрелка почти дошла.</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-m5</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Таинственные</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Неделя</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5-m5</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/1</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Десятый круг</t>
+        </is>
+      </c>
+      <c r="G177" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Дойти с кланом до десятого круга кланового босса за неделю</t>
+        </is>
+      </c>
+      <c r="H177">
+        <v>1</v>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5TenthCircle</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ритуалы</t>
+        </is>
+      </c>
+      <c r="K177">
+        <v>1</v>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">первородная</t>
+        </is>
+      </c>
+      <c r="N177">
+        <v>223</v>
+      </c>
+      <c r="O177" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Дальше, чем ходили прежде.</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-cb-1</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эхо</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-cb</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/4</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные · VI · 1</t>
+        </is>
+      </c>
+      <c r="G178" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Победить 75 призванных врагов силы VI</t>
+        </is>
+      </c>
+      <c r="H178">
+        <v>75</v>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Победы над призванными врагами силы VI</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные враги</t>
+        </is>
+      </c>
+      <c r="K178">
+        <v>1</v>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">первородная</t>
+        </is>
+      </c>
+      <c r="M178">
+        <v>1293</v>
+      </c>
+      <c r="N178">
+        <v>515</v>
+      </c>
+      <c r="O178" s="3"/>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-cb-2</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эхо</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-cb</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2/4</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные · VI · 2</t>
+        </is>
+      </c>
+      <c r="G179" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Победить 150 призванных врагов силы VI</t>
+        </is>
+      </c>
+      <c r="H179">
+        <v>150</v>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Победы над призванными врагами силы VI</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные враги</t>
+        </is>
+      </c>
+      <c r="K179">
+        <v>1</v>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="M179">
+        <v>1443</v>
+      </c>
+      <c r="N179">
+        <v>571</v>
+      </c>
+      <c r="O179" s="3"/>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-cb-3</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эхо</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-cb</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные · VI · 3</t>
+        </is>
+      </c>
+      <c r="G180" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Победить 300 призванных врагов силы VI</t>
+        </is>
+      </c>
+      <c r="H180">
+        <v>300</v>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Победы над призванными врагами силы VI</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные враги</t>
+        </is>
+      </c>
+      <c r="K180">
+        <v>1</v>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="M180">
+        <v>1743</v>
+      </c>
+      <c r="N180">
+        <v>684</v>
+      </c>
+      <c r="O180" s="3"/>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-cb-4</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эхо</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-cb</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные · VI · 4</t>
+        </is>
+      </c>
+      <c r="G181" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Победить 400 призванных врагов силы VI</t>
+        </is>
+      </c>
+      <c r="H181">
+        <v>400</v>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Победы над призванными врагами силы VI</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные враги</t>
+        </is>
+      </c>
+      <c r="K181">
+        <v>1</v>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="M181">
+        <v>1943</v>
+      </c>
+      <c r="N181">
+        <v>759</v>
+      </c>
+      <c r="O181" s="3"/>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-aw-1</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эхо</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-aw</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/2</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пробуждённые · VI · 1</t>
+        </is>
+      </c>
+      <c r="G182" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Победить 3 Пробуждённых в цикле VI</t>
+        </is>
+      </c>
+      <c r="H182">
+        <v>3</v>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Победы над Пробуждёнными в цикле VI</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные враги</t>
+        </is>
+      </c>
+      <c r="K182">
+        <v>1</v>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="M182">
+        <v>1535</v>
+      </c>
+      <c r="N182">
+        <v>635</v>
+      </c>
+      <c r="O182" s="3"/>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-aw-2</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эхо</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-aw</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2/2</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пробуждённые · VI · 2</t>
+        </is>
+      </c>
+      <c r="G183" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Победить 6 Пробуждённых в цикле VI</t>
+        </is>
+      </c>
+      <c r="H183">
+        <v>6</v>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Победы над Пробуждёнными в цикле VI</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные враги</t>
+        </is>
+      </c>
+      <c r="K183">
+        <v>1</v>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="M183">
+        <v>1927</v>
+      </c>
+      <c r="O183" s="3"/>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-run-1</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ремесло</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-run</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/6</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Места ремесла · VI · 1</t>
+        </is>
+      </c>
+      <c r="G184" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пройти крафтовые места цикла VI 4 500 раз</t>
+        </is>
+      </c>
+      <c r="H184">
+        <v>4500</v>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Забеги в крафтовые места цикла VI</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ресурс крафтового места</t>
+        </is>
+      </c>
+      <c r="K184">
+        <v>1</v>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">первородная</t>
+        </is>
+      </c>
+      <c r="M184">
+        <v>1366</v>
+      </c>
+      <c r="N184">
+        <v>542</v>
+      </c>
+      <c r="O184" s="3"/>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-run-2</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ремесло</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-run</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2/6</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Места ремесла · VI · 2</t>
+        </is>
+      </c>
+      <c r="G185" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пройти крафтовые места цикла VI 7 500 раз</t>
+        </is>
+      </c>
+      <c r="H185">
+        <v>7500</v>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Забеги в крафтовые места цикла VI</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ресурс крафтового места</t>
+        </is>
+      </c>
+      <c r="K185">
+        <v>1</v>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="M185">
+        <v>1514</v>
+      </c>
+      <c r="N185">
+        <v>597</v>
+      </c>
+      <c r="O185" s="3"/>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-run-3</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ремесло</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-run</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/6</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Места ремесла · VI · 3</t>
+        </is>
+      </c>
+      <c r="G186" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пройти крафтовые места цикла VI 12 500 раз</t>
+        </is>
+      </c>
+      <c r="H186">
+        <v>12500</v>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Забеги в крафтовые места цикла VI</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ресурс крафтового места</t>
+        </is>
+      </c>
+      <c r="K186">
+        <v>1</v>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="M186">
+        <v>1761</v>
+      </c>
+      <c r="N186">
+        <v>690</v>
+      </c>
+      <c r="O186" s="3"/>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-run-4</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ремесло</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-run</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/6</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Места ремесла · VI · 4</t>
+        </is>
+      </c>
+      <c r="G187" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пройти крафтовые места цикла VI 13 000 раз</t>
+        </is>
+      </c>
+      <c r="H187">
+        <v>13000</v>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Забеги в крафтовые места цикла VI</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ресурс крафтового места</t>
+        </is>
+      </c>
+      <c r="K187">
+        <v>1</v>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="M187">
+        <v>1785</v>
+      </c>
+      <c r="N187">
+        <v>699</v>
+      </c>
+      <c r="O187" s="3"/>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-run-5</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ремесло</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-run</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5/6</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Места ремесла · VI · 5</t>
+        </is>
+      </c>
+      <c r="G188" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пройти крафтовые места цикла VI 14 500 раз</t>
+        </is>
+      </c>
+      <c r="H188">
+        <v>14500</v>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Забеги в крафтовые места цикла VI</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Базовые ресурсы</t>
+        </is>
+      </c>
+      <c r="K188">
+        <v>1</v>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="M188">
+        <v>1860</v>
+      </c>
+      <c r="N188">
+        <v>727</v>
+      </c>
+      <c r="O188" s="3"/>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-run-6</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ремесло</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-run</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6/6</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Места ремесла · VI · 6</t>
+        </is>
+      </c>
+      <c r="G189" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пройти крафтовые места цикла VI 15 000 раз</t>
+        </is>
+      </c>
+      <c r="H189">
+        <v>15000</v>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Забеги в крафтовые места цикла VI</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Базовые ресурсы</t>
+        </is>
+      </c>
+      <c r="K189">
+        <v>1</v>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="M189">
+        <v>1884</v>
+      </c>
+      <c r="N189">
+        <v>736</v>
+      </c>
+      <c r="O189" s="3"/>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-rec-1</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ремесло</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-rec</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/1</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Книга цикла · VI</t>
+        </is>
+      </c>
+      <c r="G190" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Найти 50 рецептов цикла VI</t>
+        </is>
+      </c>
+      <c r="H190">
+        <v>50</v>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рецепты цикла VI в книге</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Вторая находка места</t>
+        </is>
+      </c>
+      <c r="K190">
+        <v>1</v>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">первородная</t>
+        </is>
+      </c>
+      <c r="M190">
+        <v>1322</v>
+      </c>
+      <c r="N190">
+        <v>546</v>
+      </c>
+      <c r="O190" s="3"/>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-circ-1</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Неделя</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-circ</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/2</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Круг за кругом · VI · 1</t>
+        </is>
+      </c>
+      <c r="G191" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Закрыть с кланом 250 кругов кланового босса в цикле VI</t>
+        </is>
+      </c>
+      <c r="H191">
+        <v>250</v>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Круги кланового босса, закрытые кланом в цикле VI</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ритуалы</t>
+        </is>
+      </c>
+      <c r="K191">
+        <v>1</v>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">первородная</t>
+        </is>
+      </c>
+      <c r="M191">
+        <v>1393</v>
+      </c>
+      <c r="N191">
+        <v>708</v>
+      </c>
+      <c r="O191" s="3"/>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-circ-2</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Неделя</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-circ</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2/2</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Круг за кругом · VI · 2</t>
+        </is>
+      </c>
+      <c r="G192" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Закрыть с кланом 500 кругов кланового босса в цикле VI</t>
+        </is>
+      </c>
+      <c r="H192">
+        <v>500</v>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Круги кланового босса, закрытые кланом в цикле VI</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ритуалы</t>
+        </is>
+      </c>
+      <c r="K192">
+        <v>1</v>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="M192">
+        <v>1643</v>
+      </c>
+      <c r="O192" s="3"/>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-step-1</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Неделя</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-step</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/3</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ступень за ступенью · VI · 1</t>
+        </is>
+      </c>
+      <c r="G193" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Взять в недельных режимах 1 250 ступеней полосы цикла VI</t>
+        </is>
+      </c>
+      <c r="H193">
+        <v>1250</v>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ступени полосы цикла VI, взятые в недельных режимах</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Календарь</t>
+        </is>
+      </c>
+      <c r="K193">
+        <v>1</v>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="M193">
+        <v>1560</v>
+      </c>
+      <c r="N193">
+        <v>760</v>
+      </c>
+      <c r="O193" s="3"/>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-step-2</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Неделя</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-step</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2/3</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ступень за ступенью · VI · 2</t>
+        </is>
+      </c>
+      <c r="G194" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Взять в недельных режимах 1 750 ступеней полосы цикла VI</t>
+        </is>
+      </c>
+      <c r="H194">
+        <v>1750</v>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ступени полосы цикла VI, взятые в недельных режимах</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Календарь</t>
+        </is>
+      </c>
+      <c r="K194">
+        <v>1</v>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="M194">
+        <v>1727</v>
+      </c>
+      <c r="O194" s="3"/>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-step-3</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Неделя</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-step</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/3</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ступень за ступенью · VI · 3</t>
+        </is>
+      </c>
+      <c r="G195" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Взять в недельных режимах 2 000 ступеней полосы цикла VI</t>
+        </is>
+      </c>
+      <c r="H195">
+        <v>2000</v>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ступени полосы цикла VI, взятые в недельных режимах</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Календарь</t>
+        </is>
+      </c>
+      <c r="K195">
+        <v>1</v>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="M195">
+        <v>1810</v>
+      </c>
+      <c r="O195" s="3"/>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-eq-1</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Странник</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-eq</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/4</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Арсенал цикла · VI · 1</t>
+        </is>
+      </c>
+      <c r="G196" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Получить 225 предметов снаряжения цикла VI</t>
+        </is>
+      </c>
+      <c r="H196">
+        <v>225</v>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Предметы снаряжения цикла VI</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Перековка</t>
+        </is>
+      </c>
+      <c r="K196">
+        <v>1</v>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">первородная</t>
+        </is>
+      </c>
+      <c r="M196">
+        <v>1248</v>
+      </c>
+      <c r="N196">
+        <v>540</v>
+      </c>
+      <c r="O196" s="3"/>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-eq-2</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Странник</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-eq</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2/4</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Арсенал цикла · VI · 2</t>
+        </is>
+      </c>
+      <c r="G197" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Получить 750 предметов снаряжения цикла VI</t>
+        </is>
+      </c>
+      <c r="H197">
+        <v>750</v>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Предметы снаряжения цикла VI</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Перековка</t>
+        </is>
+      </c>
+      <c r="K197">
+        <v>1</v>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="M197">
+        <v>1491</v>
+      </c>
+      <c r="N197">
+        <v>729</v>
+      </c>
+      <c r="O197" s="3"/>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-eq-3</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Странник</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-eq</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Арсенал цикла · VI · 3</t>
+        </is>
+      </c>
+      <c r="G198" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Получить 1 000 предметов снаряжения цикла VI</t>
+        </is>
+      </c>
+      <c r="H198">
+        <v>1000</v>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Предметы снаряжения цикла VI</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Перековка</t>
+        </is>
+      </c>
+      <c r="K198">
+        <v>1</v>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="M198">
+        <v>1606</v>
+      </c>
+      <c r="O198" s="3"/>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-eq-4</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Странник</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-eq</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Арсенал цикла · VI · 4</t>
+        </is>
+      </c>
+      <c r="G199" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Получить 1 500 предметов снаряжения цикла VI</t>
+        </is>
+      </c>
+      <c r="H199">
+        <v>1500</v>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Предметы снаряжения цикла VI</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Базовые ресурсы</t>
+        </is>
+      </c>
+      <c r="K199">
+        <v>1</v>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="M199">
+        <v>1838</v>
+      </c>
+      <c r="O199" s="3"/>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-tal-1</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Возрождённые</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рабочие и талисманы</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-tal</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/4</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Черты цикла · VI · 1</t>
+        </is>
+      </c>
+      <c r="G200" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Получить 50 духовных талисманов в цикле VI</t>
+        </is>
+      </c>
+      <c r="H200">
+        <v>50</v>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Духовные талисманы, полученные в цикле VI</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рабочие</t>
+        </is>
+      </c>
+      <c r="K200">
+        <v>1</v>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">первородная</t>
+        </is>
+      </c>
+      <c r="M200">
+        <v>1198</v>
+      </c>
+      <c r="N200">
+        <v>491</v>
+      </c>
+      <c r="O200" s="3"/>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-tal-2</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Возрождённые</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рабочие и талисманы</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-tal</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2/4</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Черты цикла · VI · 2</t>
+        </is>
+      </c>
+      <c r="G201" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Получить 450 духовных талисманов в цикле VI</t>
+        </is>
+      </c>
+      <c r="H201">
+        <v>450</v>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Духовные талисманы, полученные в цикле VI</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рабочие</t>
+        </is>
+      </c>
+      <c r="K201">
+        <v>1</v>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="M201">
+        <v>1630</v>
+      </c>
+      <c r="N201">
+        <v>750</v>
+      </c>
+      <c r="O201" s="3"/>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-tal-3</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Возрождённые</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рабочие и талисманы</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-tal</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Черты цикла · VI · 3</t>
+        </is>
+      </c>
+      <c r="G202" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Получить 500 духовных талисманов в цикле VI</t>
+        </is>
+      </c>
+      <c r="H202">
+        <v>500</v>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Духовные талисманы, полученные в цикле VI</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рабочие</t>
+        </is>
+      </c>
+      <c r="K202">
+        <v>1</v>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="M202">
+        <v>1684</v>
+      </c>
+      <c r="O202" s="3"/>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-tal-4</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Возрождённые</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рабочие и талисманы</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-tal</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Черты цикла · VI · 4</t>
+        </is>
+      </c>
+      <c r="G203" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Получить 700 духовных талисманов в цикле VI</t>
+        </is>
+      </c>
+      <c r="H203">
+        <v>700</v>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Духовные талисманы, полученные в цикле VI</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Уникальный ресурс</t>
+        </is>
+      </c>
+      <c r="K203">
+        <v>1</v>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="M203">
+        <v>1900</v>
+      </c>
+      <c r="O203" s="3"/>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-val-1</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Возрождённые</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Главы, ордены, пределы</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-val</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/4</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Доблесть цикла · VI · 1</t>
+        </is>
+      </c>
+      <c r="G204" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Поднять доблесть героям цикла VI 3 раза</t>
+        </is>
+      </c>
+      <c r="H204">
+        <v>3</v>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Доблесть героев цикла VI: сколько раз поднята</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Уровни героев</t>
+        </is>
+      </c>
+      <c r="K204">
+        <v>1</v>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="M204">
+        <v>1465</v>
+      </c>
+      <c r="N204">
+        <v>582</v>
+      </c>
+      <c r="O204" s="3"/>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-val-2</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Возрождённые</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Главы, ордены, пределы</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-val</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2/4</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Доблесть цикла · VI · 2</t>
+        </is>
+      </c>
+      <c r="G205" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Поднять доблесть героям цикла VI 6 раз</t>
+        </is>
+      </c>
+      <c r="H205">
+        <v>6</v>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Доблесть героев цикла VI: сколько раз поднята</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Дух за убийство</t>
+        </is>
+      </c>
+      <c r="K205">
+        <v>1</v>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="M205">
+        <v>1585</v>
+      </c>
+      <c r="N205">
+        <v>629</v>
+      </c>
+      <c r="O205" s="3"/>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-val-3</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Возрождённые</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Главы, ордены, пределы</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-val</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Доблесть цикла · VI · 3</t>
+        </is>
+      </c>
+      <c r="G206" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Поднять доблесть героям цикла VI 8 раз</t>
+        </is>
+      </c>
+      <c r="H206">
+        <v>8</v>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Доблесть героев цикла VI: сколько раз поднята</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Дух за убийство</t>
+        </is>
+      </c>
+      <c r="K206">
+        <v>1</v>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="M206">
+        <v>1664</v>
+      </c>
+      <c r="N206">
+        <v>659</v>
+      </c>
+      <c r="O206" s="3"/>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-val-4</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Возрождённые</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Главы, ордены, пределы</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-val</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Доблесть цикла · VI · 4</t>
+        </is>
+      </c>
+      <c r="G207" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Поднять доблесть героям цикла VI 9 раз</t>
+        </is>
+      </c>
+      <c r="H207">
+        <v>9</v>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Доблесть героев цикла VI: сколько раз поднята</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Золото за убийство</t>
+        </is>
+      </c>
+      <c r="K207">
+        <v>1</v>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="M207">
+        <v>1702</v>
+      </c>
+      <c r="N207">
+        <v>674</v>
+      </c>
+      <c r="O207" s="3"/>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-eh-1</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Возрождённые</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Герои</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-eh</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/3</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Герои нашествий · VI · 1</t>
+        </is>
+      </c>
+      <c r="G208" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Собрать 3 героев Эхо цикла VI</t>
+        </is>
+      </c>
+      <c r="H208">
+        <v>3</v>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Герои Эхо цикла VI, собранные из осколков</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Прах душ</t>
+        </is>
+      </c>
+      <c r="K208">
+        <v>1</v>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">первородная</t>
+        </is>
+      </c>
+      <c r="M208">
+        <v>1185</v>
+      </c>
+      <c r="N208">
+        <v>481</v>
+      </c>
+      <c r="O208" s="3"/>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-eh-2</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Возрождённые</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Герои</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-eh</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2/3</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Герои нашествий · VI · 2</t>
+        </is>
+      </c>
+      <c r="G209" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Собрать 6 героев Эхо цикла VI</t>
+        </is>
+      </c>
+      <c r="H209">
+        <v>6</v>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Герои Эхо цикла VI, собранные из осколков</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Прах душ</t>
+        </is>
+      </c>
+      <c r="K209">
+        <v>1</v>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">первородная</t>
+        </is>
+      </c>
+      <c r="M209">
+        <v>1227</v>
+      </c>
+      <c r="N209">
+        <v>504</v>
+      </c>
+      <c r="O209" s="3"/>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-eh-3</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Возрождённые</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Герои</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-eh</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/3</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Герои нашествий · VI · 3</t>
+        </is>
+      </c>
+      <c r="G210" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Собрать 9 героев Эхо цикла VI</t>
+        </is>
+      </c>
+      <c r="H210">
+        <v>9</v>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Герои Эхо цикла VI, собранные из осколков</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Прах душ</t>
+        </is>
+      </c>
+      <c r="K210">
+        <v>1</v>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">первородная</t>
+        </is>
+      </c>
+      <c r="M210">
+        <v>1269</v>
+      </c>
+      <c r="N210">
+        <v>527</v>
+      </c>
+      <c r="O210" s="3"/>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-lim-1</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Возрождённые</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Главы, ордены, пределы</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-lim</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/2</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Третий предел · VI</t>
+        </is>
+      </c>
+      <c r="G211" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пробить третий рунный предел всем пятерым героям отряда цикла VI</t>
+        </is>
+      </c>
+      <c r="H211">
+        <v>3</v>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рунный предел, пробитый у всех пятерых героев отряда цикла VI</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рунный ключ</t>
+        </is>
+      </c>
+      <c r="K211">
+        <v>1</v>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">первородная</t>
+        </is>
+      </c>
+      <c r="M211">
+        <v>1171</v>
+      </c>
+      <c r="N211">
+        <v>478</v>
+      </c>
+      <c r="O211" s="3"/>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-lim-2</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Возрождённые</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Главы, ордены, пределы</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-lim</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2/2</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пятый предел · VI</t>
+        </is>
+      </c>
+      <c r="G212" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пробить пятый рунный предел всем пятерым героям отряда цикла VI</t>
+        </is>
+      </c>
+      <c r="H212">
+        <v>5</v>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рунный предел, пробитый у всех пятерых героев отряда цикла VI</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рунный ключ</t>
+        </is>
+      </c>
+      <c r="K212">
+        <v>1</v>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">первородная</t>
+        </is>
+      </c>
+      <c r="M212">
+        <v>1345</v>
+      </c>
+      <c r="N212">
+        <v>537</v>
+      </c>
+      <c r="O212" s="3"/>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-recAll-1</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ремесло</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-recAll</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/1</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Вся книга цикла · VI</t>
+        </is>
+      </c>
+      <c r="G213" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Найти все рецепты цикла VI</t>
+        </is>
+      </c>
+      <c r="H213">
+        <v>78</v>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рецепты цикла VI в книге</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Уникальный ресурс</t>
+        </is>
+      </c>
+      <c r="K213">
+        <v>1</v>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="M213">
+        <v>1422</v>
+      </c>
+      <c r="N213">
+        <v>595</v>
+      </c>
+      <c r="O213" s="3"/>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-top-1</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Неделя</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-top</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/2</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Верх полосы · VI</t>
+        </is>
+      </c>
+      <c r="G214" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Взять верх полосы цикла VI в недельном режиме</t>
+        </is>
+      </c>
+      <c r="H214">
+        <v>1</v>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Недельные режимы, где взят верх полосы цикла VI</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Базовые ресурсы</t>
+        </is>
+      </c>
+      <c r="K214">
+        <v>1</v>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="N214">
+        <v>465</v>
+      </c>
+      <c r="O214" s="3"/>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-top-2</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Персональные</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Неделя</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-top</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2/2</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Три вершины · VI</t>
+        </is>
+      </c>
+      <c r="G215" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Взять верх полосы цикла VI в трёх недельных режимах</t>
+        </is>
+      </c>
+      <c r="H215">
+        <v>3</v>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Недельные режимы, где взят верх полосы цикла VI</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Уникальный ресурс</t>
+        </is>
+      </c>
+      <c r="K215">
+        <v>1</v>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="N215">
+        <v>465</v>
+      </c>
+      <c r="O215" s="3"/>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-m1</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Таинственные</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эхо</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-m1</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/1</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Потолок</t>
+        </is>
+      </c>
+      <c r="G216" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Взять шестую ступень полосы цикла VI в Эхо</t>
+        </is>
+      </c>
+      <c r="H216">
+        <v>1</v>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6Ceiling</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Прах душ</t>
+        </is>
+      </c>
+      <c r="K216">
+        <v>2</v>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="O216" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Выше только небо над башней.</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-m2</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Таинственные</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эхо</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-m2</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/1</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Все девять</t>
+        </is>
+      </c>
+      <c r="G217" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Победить Убер-боссов всех девяти недель рас, не выходя из цикла VI</t>
+        </is>
+      </c>
+      <c r="H217">
+        <v>1</v>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6AllNine</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Уникальный ресурс</t>
+        </is>
+      </c>
+      <c r="K217">
+        <v>2</v>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="O217" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Девять раз — и ни одной осечки.</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-m3</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Таинственные</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Главы, ордены, пределы</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-m3</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/1</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Последняя глава</t>
+        </is>
+      </c>
+      <c r="G218" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Довести героя цикла VI до личного максимума доблести</t>
+        </is>
+      </c>
+      <c r="H218">
+        <v>1</v>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6LastChapter</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Базовые ресурсы</t>
+        </is>
+      </c>
+      <c r="K218">
+        <v>1</v>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="O218" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Дальше учить нечему.</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-m4</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Таинственные</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Спуск</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-m4</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/1</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">С самого дна</t>
+        </is>
+      </c>
+      <c r="G219" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Закрыть последний биом спуска, не потеряв ни одного героя</t>
+        </is>
+      </c>
+      <c r="H219">
+        <v>1</v>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6FromBottom</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ресурс крафтового места</t>
+        </is>
+      </c>
+      <c r="K219">
+        <v>1</v>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="M219">
+        <v>1970</v>
+      </c>
+      <c r="N219">
+        <v>777</v>
+      </c>
+      <c r="O219" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Никто не остался внизу.</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-m5</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Таинственные</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Неделя</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6-m5</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/1</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Двенадцатый круг</t>
+        </is>
+      </c>
+      <c r="G220" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Дойти с кланом до двенадцатого круга кланового босса за неделю</t>
+        </is>
+      </c>
+      <c r="H220">
+        <v>1</v>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6TwelfthCircle</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ритуалы</t>
+        </is>
+      </c>
+      <c r="K220">
+        <v>1</v>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">вневременная</t>
+        </is>
+      </c>
+      <c r="O220" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Круг, которого не ждали.</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P103"/>
+  <autoFilter ref="A1:R220"/>
 </worksheet>
 </file>
 
@@ -8421,7 +16934,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -8752,7 +17265,67 @@
         <v>20</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">place</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ресурс крафтового места</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">шанс ресурса крафтового места за этаж выше на {v} % (относительно)</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">find2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Вторая находка места</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">шанс второй находки крафтового места выше на {v} % (относительно)</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">summon</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные враги</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+{v} % духа и золота с призванных врагов</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D16"/>
+  <autoFilter ref="A1:D19"/>
 </worksheet>
 </file>